--- a/docs/downloads/11/tbl_cata_prevalence_alaotra_tous.xlsx
+++ b/docs/downloads/11/tbl_cata_prevalence_alaotra_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2">
@@ -395,7 +395,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B3">
@@ -411,7 +411,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B4">
@@ -427,7 +427,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B5">
@@ -443,7 +443,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B6">
@@ -459,7 +459,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B7">
@@ -475,7 +475,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B8">
@@ -491,7 +491,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B9">
@@ -507,7 +507,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B10">
